--- a/data/trans_orig/IP21-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP21-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1428</t>
+          <t>1353</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7869</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2305</t>
+          <t>2278</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>10935</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5195</t>
+          <t>5023</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14952</t>
+          <t>15481</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,31%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>130857</t>
+          <t>130628</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137298</t>
+          <t>137373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>142395</t>
+          <t>142142</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>150772</t>
+          <t>150799</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276851</t>
+          <t>276322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>286608</t>
+          <t>286780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,28%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17966</t>
+          <t>16657</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>5820</t>
+          <t>5782</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15229</t>
+          <t>15519</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14904</t>
+          <t>14940</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28314</t>
+          <t>28248</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>177197</t>
+          <t>178506</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>188341</t>
+          <t>188412</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>196913</t>
+          <t>196623</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>206322</t>
+          <t>206360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>92,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>378991</t>
+          <t>379057</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>392401</t>
+          <t>392365</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,05%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11358</t>
+          <t>11198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3950</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12607</t>
+          <t>12929</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9075</t>
+          <t>8969</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20521</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,97%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>126459</t>
+          <t>126619</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>134375</t>
+          <t>134569</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,76%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>137050</t>
+          <t>136728</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>145707</t>
+          <t>145646</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,32%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>266953</t>
+          <t>267430</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>278399</t>
+          <t>278505</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,88%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1469</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7604</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6257</t>
+          <t>6582</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17139</t>
+          <t>16938</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9169</t>
+          <t>9214</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21325</t>
+          <t>21855</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>201656</t>
+          <t>201711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>207873</t>
+          <t>207846</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>190685</t>
+          <t>190886</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201567</t>
+          <t>201242</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>395814</t>
+          <t>395284</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>407970</t>
+          <t>407925</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,79%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>18367</t>
+          <t>18081</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>34016</t>
+          <t>33917</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25312</t>
+          <t>24286</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42986</t>
+          <t>43268</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47014</t>
+          <t>47626</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>71123</t>
+          <t>72464</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>647005</t>
+          <t>647104</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>662654</t>
+          <t>662940</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>679714</t>
+          <t>679432</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>697388</t>
+          <t>698414</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1332598</t>
+          <t>1331257</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1356707</t>
+          <t>1356095</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,93%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,61%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1403</t>
+          <t>1434</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8176</t>
+          <t>8372</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3223</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12715</t>
+          <t>13193</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6729</t>
+          <t>6689</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17673</t>
+          <t>17993</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,12%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>131181</t>
+          <t>130985</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>137954</t>
+          <t>137923</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141969</t>
+          <t>141491</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>151461</t>
+          <t>151502</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276368</t>
+          <t>276048</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287312</t>
+          <t>287352</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6293</t>
+          <t>5946</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16705</t>
+          <t>16439</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3321</t>
+          <t>3326</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11931</t>
+          <t>11954</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11285</t>
+          <t>11644</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24388</t>
+          <t>25148</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>189653</t>
+          <t>189919</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>200065</t>
+          <t>200412</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>211234</t>
+          <t>211211</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>219844</t>
+          <t>219839</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>405135</t>
+          <t>404375</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>418238</t>
+          <t>417879</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,37%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3027</t>
+          <t>2839</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>11094</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5322</t>
+          <t>5868</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15703</t>
+          <t>15646</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10395</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22728</t>
+          <t>23045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>144499</t>
+          <t>144282</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>152349</t>
+          <t>152537</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,0%</t>
+          <t>92,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>149304</t>
+          <t>149361</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>159685</t>
+          <t>159139</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,44%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>297655</t>
+          <t>297338</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>309988</t>
+          <t>310095</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,79%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3825</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>14132</t>
+          <t>14654</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>5259</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16252</t>
+          <t>16219</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12033</t>
+          <t>11786</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26603</t>
+          <t>26176</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>196168</t>
+          <t>195646</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>206475</t>
+          <t>206071</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>190806</t>
+          <t>190839</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>201826</t>
+          <t>201799</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,15%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>390755</t>
+          <t>391182</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>405325</t>
+          <t>405572</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,18%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>20920</t>
+          <t>20332</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>38098</t>
+          <t>37653</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25045</t>
+          <t>25249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42564</t>
+          <t>43870</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>51365</t>
+          <t>49961</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74303</t>
+          <t>76239</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>673293</t>
+          <t>673738</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>690471</t>
+          <t>691059</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>707350</t>
+          <t>706044</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>724869</t>
+          <t>724665</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1387002</t>
+          <t>1385066</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1409940</t>
+          <t>1411344</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1351</t>
+          <t>1400</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8421</t>
+          <t>8132</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3106</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12654</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6318</t>
+          <t>6177</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16728</t>
+          <t>17584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,24%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>125286</t>
+          <t>125575</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>132356</t>
+          <t>132307</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>135422</t>
+          <t>136423</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144970</t>
+          <t>144847</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,9%</t>
+          <t>97,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>265055</t>
+          <t>264199</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>275465</t>
+          <t>275606</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5329</t>
+          <t>5311</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14320</t>
+          <t>14589</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2783</t>
+          <t>2999</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11278</t>
+          <t>10882</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9830</t>
+          <t>9971</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21424</t>
+          <t>22283</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,17%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>192391</t>
+          <t>192122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>201382</t>
+          <t>201400</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>92,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>213081</t>
+          <t>213477</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>221576</t>
+          <t>221360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>409646</t>
+          <t>408787</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>421240</t>
+          <t>421099</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,69%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>884</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>7572</t>
+          <t>7296</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3008</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11877</t>
+          <t>10684</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,31%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148954</t>
+          <t>149575</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>154859</t>
+          <t>154884</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>159101</t>
+          <t>159377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>165788</t>
+          <t>165789</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,46%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>310793</t>
+          <t>311986</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319662</t>
+          <t>320110</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2200</t>
+          <t>2275</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9863</t>
+          <t>10379</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2215</t>
+          <t>2090</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5101</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16220</t>
+          <t>16844</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>196870</t>
+          <t>196354</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>204533</t>
+          <t>204458</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>195725</t>
+          <t>195860</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>203521</t>
+          <t>203646</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>396249</t>
+          <t>395625</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>407368</t>
+          <t>406795</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14921</t>
+          <t>15132</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>29168</t>
+          <t>29261</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>13633</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>29730</t>
+          <t>29319</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32805</t>
+          <t>32566</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53651</t>
+          <t>54318</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>673980</t>
+          <t>673887</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>688227</t>
+          <t>688016</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>715114</t>
+          <t>715525</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>730685</t>
+          <t>731211</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1394341</t>
+          <t>1393674</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1415187</t>
+          <t>1415426</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,75%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>536</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>4966</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1185</t>
+          <t>1120</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7599</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2424</t>
+          <t>2595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9913</t>
+          <t>9498</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>112004</t>
+          <t>112314</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116719</t>
+          <t>116744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>132813</t>
+          <t>133246</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139227</t>
+          <t>139292</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>247780</t>
+          <t>248195</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255269</t>
+          <t>255098</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>98,99%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>586</t>
+          <t>560</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1819</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>10226</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3313</t>
+          <t>3309</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13681</t>
+          <t>13306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>2,99%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>185069</t>
+          <t>184955</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>189926</t>
+          <t>189952</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,14%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>243903</t>
+          <t>244809</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>253216</t>
+          <t>253310</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>431867</t>
+          <t>432242</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442235</t>
+          <t>442239</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,7 +7115,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1599</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10248</t>
+          <t>9943</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1840</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9929</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>178921</t>
+          <t>179226</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>187638</t>
+          <t>187570</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,58%</t>
+          <t>94,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>364526</t>
+          <t>364975</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>372615</t>
+          <t>372426</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,46%</t>
         </is>
       </c>
     </row>
@@ -7608,7 +7608,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>3721</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1726</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9187</t>
+          <t>9194</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,7 +7653,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2431</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10454</t>
+          <t>9530</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>164118</t>
+          <t>164241</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>172051</t>
+          <t>172044</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179512</t>
+          <t>179332</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>98,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>338747</t>
+          <t>339671</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>346770</t>
+          <t>347005</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5003</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15333</t>
+          <t>15592</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7477</t>
+          <t>7426</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>20256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>14607</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30799</t>
+          <t>29838</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>649591</t>
+          <t>649332</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>659921</t>
+          <t>659446</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>742456</t>
+          <t>741716</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754495</t>
+          <t>754546</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1396097</t>
+          <t>1397058</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1412632</t>
+          <t>1412289</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,0%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP21-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP21-Habitat-trans_orig.xlsx
@@ -538,13 +538,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo ingresado en un hospital en los últimos 12 meses en 2007 (tasa de respuesta: 100,0%)</t>
+          <t>Menores según si estuvo ingresado/a, al menos una noche, en un hospital en los últimos 12 meses en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5268</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2295</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>10549</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>3,44%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3860</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1353</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8098</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1431</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>7836</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,78%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>5,84%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>5268</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>2278</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>10935</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5023</t>
+          <t>4991</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15481</t>
+          <t>14883</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>147809</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>142528</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>150782</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>96,56%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,11%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>197</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>134866</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>130628</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>137373</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>130890</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>137295</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,22%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>94,16%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,03%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>147809</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>142142</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>150799</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>94,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276322</t>
+          <t>276920</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>286780</t>
+          <t>286812</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,29%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>153077</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>203</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>138726</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>153077</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>9739</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>5198</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>15492</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,45%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,3%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>11107</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6751</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16657</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6874</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16762</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,69%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>3,46%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,53%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>9739</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>5782</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>15519</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14940</t>
+          <t>15006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>28248</t>
+          <t>28432</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,98%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>202403</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>196650</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>206944</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,41%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,7%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,55%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>294</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>184056</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>178506</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>188412</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>178401</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>188289</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,31%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>91,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>96,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>202403</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>196623</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>206360</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,68%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>379057</t>
+          <t>378873</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>392365</t>
+          <t>392299</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,32%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>212142</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>312</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>195163</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>322</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>212142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1414,67 +1414,67 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>7375</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4040</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12827</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,93%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2,7%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>6706</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3248</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11198</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3340</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>11365</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>4,87%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>8,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7375</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4011</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12929</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>4,93%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8969</t>
+          <t>9006</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20044</t>
+          <t>21014</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>142282</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>136830</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>145617</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>95,07%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>91,43%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>97,3%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>131111</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>126619</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>134569</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>126452</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>134477</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>95,13%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>91,87%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,64%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>142282</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>136728</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>145646</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>95,07%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,32%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>267430</t>
+          <t>266460</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>278505</t>
+          <t>278468</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>93,03%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,87%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>149657</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>137817</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>149657</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10771</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6701</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>16805</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>5,18%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8,09%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3738</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1469</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7604</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1457</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8838</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,7%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,63%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>10771</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>6582</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16938</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>5,18%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>3,17%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9214</t>
+          <t>9129</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>21855</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,92%</t>
         </is>
       </c>
     </row>
@@ -1865,74 +1865,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>197053</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>191019</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>201123</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>94,82%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>91,91%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>96,78%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>205577</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>201711</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>207846</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>200477</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>207858</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>98,21%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,37%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>95,78%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,3%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>197053</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>190886</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>201242</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>94,82%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>91,85%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>96,83%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>559</t>
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>395284</t>
+          <t>396631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>407925</t>
+          <t>408010</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>95,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>274</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>209315</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207824</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33154</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24714</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44527</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,59%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,42%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>25411</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>18081</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>33917</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>18554</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>34256</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,73%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>33154</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>24286</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>43268</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>47626</t>
+          <t>47391</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>72464</t>
+          <t>71554</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1037</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>689546</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>678173</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>697986</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,41%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>93,84%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,58%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>978</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>655610</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>647104</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>662940</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>646765</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>662467</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,27%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,02%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,34%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1037</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>689546</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>679432</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>698414</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,41%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,01%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1331257</t>
+          <t>1332167</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1356095</t>
+          <t>1356330</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,62%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>722700</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>722700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2485,13 +2485,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo ingresado en un hospital en los últimos 12 meses en 2012 (tasa de respuesta: 99,76%)</t>
+          <t>Menores según si estuvo ingresado/a, al menos una noche, en un hospital en los últimos 12 meses en 2012 (tasa de respuesta: 99,76%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6925</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3290</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>13183</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,48%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,52%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>4114</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1434</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8372</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1372</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8192</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,95%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,01%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6925</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3182</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>13193</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,48%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6689</t>
+          <t>6220</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17993</t>
+          <t>17059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,8%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>147759</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>141501</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>151394</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,52%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,48%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>135243</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>130985</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>137923</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>131165</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>137985</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,05%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,99%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>147759</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>141491</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>151502</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,52%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>276048</t>
+          <t>276982</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287352</t>
+          <t>287821</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,88%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>139357</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6628</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3283</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11498</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5,15%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>10501</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5946</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>16439</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>6056</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>16287</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>5,09%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,88%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>6628</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>3326</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>11954</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>11644</t>
+          <t>10884</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>25148</t>
+          <t>24084</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,61%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>216537</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>211667</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>219882</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,03%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>94,85%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,53%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>195857</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>189919</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>200412</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>190071</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>200302</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>94,91%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,12%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>313</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>216537</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>211211</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>219839</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,64%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>97,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>404375</t>
+          <t>405439</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>417879</t>
+          <t>418639</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>223165</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>223165</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>223165</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>319</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206358</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>223165</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>223165</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>223165</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>9776</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>5877</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>16013</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,92%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,56%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>9,7%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>5868</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2839</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11094</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2589</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>10552</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>3,78%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,14%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>9776</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>5868</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>15646</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,92%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>10288</t>
+          <t>9876</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>23045</t>
+          <t>22511</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,03%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>155231</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>148994</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>159130</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>94,08%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>90,3%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,44%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>149508</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>144282</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>152537</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>144824</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>152787</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>96,22%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>92,86%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>155231</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>149361</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>159139</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>94,08%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>93,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>297338</t>
+          <t>297872</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>310095</t>
+          <t>310507</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,92%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>165007</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>165007</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>165007</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155376</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>165007</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>165007</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>165007</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9893</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>5276</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>15846</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,65%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>8221</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4229</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>14654</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4278</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14365</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,91%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,97%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>9893</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>5259</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>16219</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11786</t>
+          <t>12143</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26176</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>197165</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>191212</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>201782</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>95,22%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>92,35%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>97,45%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>264</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>202079</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>195646</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>206071</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>195935</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>206022</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,09%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,03%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,99%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>197165</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>190839</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>201799</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>95,22%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>391182</t>
+          <t>390738</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>405572</t>
+          <t>405215</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,09%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>281</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>207058</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>207058</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>207058</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>275</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>210300</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>281</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>207058</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>207058</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>207058</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33222</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>24790</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>44312</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3,31%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5,91%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>28704</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>20332</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>37653</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>20624</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>38603</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>4,03%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,29%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>33222</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>25249</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>43870</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>4,43%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>49961</t>
+          <t>49795</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>76239</t>
+          <t>75301</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1022</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>716692</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>705602</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>725124</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>95,57%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>94,09%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>96,69%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>983</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>682687</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>673738</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>691059</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>672788</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>690767</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>95,97%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,71%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,14%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1022</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>716692</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>706044</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>724665</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>95,57%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1385066</t>
+          <t>1386004</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1411344</t>
+          <t>1411510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,59%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1069</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>749914</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>749914</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>749914</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1025</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>711391</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1069</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>749914</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>749914</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>749914</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,13 +4432,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo ingresado en un hospital en los últimos 12 meses en 2016 (tasa de respuesta: 99,91%)</t>
+          <t>Menores según si estuvo ingresado/a, al menos una noche, en un hospital en los últimos 12 meses en 2016 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>6752</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>3099</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>12336</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>8,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>3952</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1400</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>8132</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1351</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>8356</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,96%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,08%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>6752</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>3229</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11653</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>4,56%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6462</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17584</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>141324</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>135740</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>144977</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>95,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>91,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>97,91%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>181</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>129755</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>125575</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>132307</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>125351</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>132356</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,04%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>93,92%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>141324</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>136423</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>144847</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>95,44%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,82%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>264199</t>
+          <t>264260</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>275606</t>
+          <t>275321</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>148076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>195</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>148076</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>5991</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2892</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10721</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,67%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,29%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>9088</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>5311</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>14589</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>5128</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>14127</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>4,4%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,57%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>5991</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2999</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>10882</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9971</t>
+          <t>9427</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>22283</t>
+          <t>21860</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>218368</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>213638</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>221467</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>98,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>318</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>197623</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>192122</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>201400</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>192584</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>201583</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>95,6%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>92,94%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>97,43%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>218368</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>213477</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>221360</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,33%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>93,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>97,52%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>408787</t>
+          <t>409210</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>421099</t>
+          <t>421643</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,83%</t>
+          <t>94,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,81%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>333</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>206711</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>206711</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>206711</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2965</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>6859</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3024</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1113</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6422</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1148</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7397</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,94%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>2965</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>884</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>7296</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,78%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2560</t>
+          <t>2856</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10684</t>
+          <t>11097</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,44%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>163708</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>159814</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>165802</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,22%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,88%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>99,48%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>152973</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>149575</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>154884</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>148600</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>154849</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>98,06%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>95,88%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,29%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>244</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>163708</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>159377</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>165789</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,22%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>311986</t>
+          <t>311573</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>320110</t>
+          <t>319814</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>259</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>155997</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5651,67 +5651,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>4990</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2136</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>9754</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,74%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>5165</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2275</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>10379</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2202</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>9742</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>2,5%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>5,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4990</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2090</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9876</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5674</t>
+          <t>5772</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>16844</t>
+          <t>16793</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>283</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>200746</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>195982</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>203600</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,26%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>273</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>201568</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>196354</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>204458</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>196991</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>204531</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>97,5%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>94,98%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,9%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>283</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>200746</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>195860</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>203646</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,57%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,93%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>395625</t>
+          <t>395676</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>406795</t>
+          <t>406697</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>205736</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>206733</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>206733</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>206733</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>205736</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20697</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14379</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>29947</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,93%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,02%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>21228</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15132</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>29261</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>15183</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>29522</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,02%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>13633</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>29319</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,78%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>32566</t>
+          <t>32181</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>52655</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>1036</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>724147</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>714897</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>730465</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>97,22%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,98%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,07%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>1026</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>681920</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>673887</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>688016</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>673626</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>687965</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,98%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>95,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,85%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>1036</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>724147</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>715525</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>731211</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>97,22%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1393674</t>
+          <t>1395337</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1415426</t>
+          <t>1415811</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1059</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>703148</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>703148</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>703148</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6379,13 +6379,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según si estuvo ingresado en un hospital en los últimos 12 meses en 2023 (tasa de respuesta: 99,95%)</t>
+          <t>Menores según si estuvo ingresado/a, al menos una noche, en un hospital en los últimos 12 meses en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2684</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>883</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6183</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,13%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,91%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>1993</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4966</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,23%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3122</t>
+          <t>1919</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1120</t>
+          <t>535</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7166</t>
+          <t>4934</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>5115</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2595</t>
+          <t>2227</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>9498</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>123222</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>119723</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>125023</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,87%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,09%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,3%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>115287</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>112314</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>116744</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>98,3%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,77%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>137290</t>
+          <t>119152</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>133246</t>
+          <t>116137</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>139292</t>
+          <t>120536</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>98,42%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>252578</t>
+          <t>242374</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>248195</t>
+          <t>238393</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>255098</t>
+          <t>244750</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1456</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11598</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,91%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1947</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5557</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>1797</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1725</t>
+          <t>573</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>10226</t>
+          <t>5619</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>6722</t>
+          <t>6323</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3309</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>13306</t>
+          <t>12970</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>232680</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>225608</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>235750</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,09%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,39%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>277</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>188565</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>184955</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>189952</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>97,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>250260</t>
+          <t>182616</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>244809</t>
+          <t>178794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>253310</t>
+          <t>183840</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>438826</t>
+          <t>415296</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>432242</t>
+          <t>408649</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>442239</t>
+          <t>418863</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,35%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,72 +7250,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>4536</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1599</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>9943</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,26%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1821</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9015</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4536</t>
+          <t>4418</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>218</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>184633</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>179226</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>187570</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>97,6%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,74%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,15%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>151427</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>146830</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>154024</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>—%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>369919</t>
+          <t>319768</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>364975</t>
+          <t>315640</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>372426</t>
+          <t>322368</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,79%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,44%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>189169</t>
+          <t>168341</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>189169</t>
+          <t>168341</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>189169</t>
+          <t>168341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>155845</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>155845</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>155845</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>374455</t>
+          <t>324186</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>374455</t>
+          <t>324186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>374455</t>
+          <t>324186</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4115</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1636</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8280</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>739</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3721</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3134</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4563</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1906</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9194</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>1,05%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,22 +7668,22 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>5302</t>
+          <t>4817</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2196</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9530</t>
+          <t>9158</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -7706,74 +7706,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>165261</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>161096</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>167740</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>97,57%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,11%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>167223</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>164241</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>97,78%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>166443</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>164011</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>167145</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>99,58%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,12%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>176675</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>172044</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>179332</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>97,48%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>94,93%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>98,95%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>470</t>
@@ -7781,27 +7781,27 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>343899</t>
+          <t>331704</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>339671</t>
+          <t>327363</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>347005</t>
+          <t>334398</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11325</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>6636</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>18992</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,95%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>9215</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5478</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15592</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,34%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12461</t>
+          <t>8835</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7426</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20256</t>
+          <t>14576</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,17 +8011,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>21675</t>
+          <t>20160</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>14607</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>29838</t>
+          <t>29765</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>689504</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>681837</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>694193</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,38%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>926</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>655709</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>649332</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>659446</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,66%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>959</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>749511</t>
+          <t>619639</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>741716</t>
+          <t>613898</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754546</t>
+          <t>623645</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,17 +8124,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1405221</t>
+          <t>1309143</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1397058</t>
+          <t>1299538</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1412289</t>
+          <t>1315343</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>941</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>664924</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>664924</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>664924</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628474</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628474</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>628474</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1426896</t>
+          <t>1329303</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1426896</t>
+          <t>1329303</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1426896</t>
+          <t>1329303</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
